--- a/participantList.xlsx
+++ b/participantList.xlsx
@@ -420,13 +420,13 @@
         <v>否</v>
       </c>
       <c r="J2" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="K2" t="str">
         <v>否</v>
       </c>
       <c r="L2" t="str">
-        <v>113.104.203.129</v>
+        <v>113.91.140.129</v>
       </c>
       <c r="M2" t="str">
         <v>192.168.11.129</v>
@@ -453,13 +453,13 @@
         <v>OBS Virtual Camera</v>
       </c>
       <c r="U2" t="str">
-        <v>2024.10.08 07:48:29 (GMT+08:00)</v>
+        <v>2024.09.29 00:57:12 (GMT+08:00)</v>
       </c>
       <c r="V2" t="str">
-        <v>2024.10.09 04:10:06 (GMT+08:00)</v>
+        <v>2024.09.30 00:54:17 (GMT+08:00)</v>
       </c>
       <c r="W2" t="str">
-        <v>20:21:37</v>
+        <v>23:57:05</v>
       </c>
       <c r="X2" t="str">
         <v>主持人结束会议</v>
@@ -467,11 +467,9 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>田嘉尧</v>
-      </c>
-      <c r="B3" t="str">
-        <v>飞书个人用户</v>
-      </c>
+        <v>李德胜</v>
+      </c>
+      <c r="B3" t="str"/>
       <c r="C3" t="str"/>
       <c r="D3" t="str"/>
       <c r="E3" t="str"/>
@@ -488,7 +486,7 @@
         <v>否</v>
       </c>
       <c r="J3" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
         <v>否</v>
@@ -512,22 +510,22 @@
         <v>udp</v>
       </c>
       <c r="R3" t="str">
-        <v>与系统一致（麦克风阵列 (Realtek(R) Audio)）</v>
+        <v>与系统一致（麦克风阵列 (适用于数字麦克风的英特尔® 智音技术)）</v>
       </c>
       <c r="S3" t="str">
         <v>与系统一致（扬声器 (Realtek(R) Audio)）</v>
       </c>
       <c r="T3" t="str">
-        <v>USB2.0 HD UVC WebCam</v>
+        <v>XiaoMi USB 2.0 Webcam</v>
       </c>
       <c r="U3" t="str">
-        <v>2024.10.08 07:49:20 (GMT+08:00)</v>
+        <v>2024.09.29 00:57:39 (GMT+08:00)</v>
       </c>
       <c r="V3" t="str">
-        <v>2024.10.08 22:15:25 (GMT+08:00)</v>
+        <v>2024.09.29 02:28:31 (GMT+08:00)</v>
       </c>
       <c r="W3" t="str">
-        <v>14:26:05</v>
+        <v>01:30:52</v>
       </c>
       <c r="X3" t="str">
         <v>主动挂断</v>
@@ -535,7 +533,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>杜海云</v>
+        <v>王家瑶</v>
       </c>
       <c r="B4" t="str"/>
       <c r="C4" t="str"/>
@@ -587,13 +585,13 @@
         <v>front_camera</v>
       </c>
       <c r="U4" t="str">
-        <v>2024.10.08 07:59:24 (GMT+08:00)</v>
+        <v>2024.09.29 08:07:31 (GMT+08:00)</v>
       </c>
       <c r="V4" t="str">
-        <v>2024.10.08 22:48:00 (GMT+08:00)</v>
+        <v>2024.09.29 23:04:55 (GMT+08:00)</v>
       </c>
       <c r="W4" t="str">
-        <v>14:48:36</v>
+        <v>14:57:24</v>
       </c>
       <c r="X4" t="str">
         <v>主动挂断</v>
@@ -601,7 +599,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ashore</v>
+        <v>杜海云</v>
       </c>
       <c r="B5" t="str"/>
       <c r="C5" t="str"/>
@@ -638,7 +636,7 @@
         <v>不支持查看外部参会者的敏感信息</v>
       </c>
       <c r="P5" t="str">
-        <v>5G</v>
+        <v>wifi</v>
       </c>
       <c r="Q5" t="str">
         <v>udp</v>
@@ -653,23 +651,25 @@
         <v>front_camera</v>
       </c>
       <c r="U5" t="str">
-        <v>2024.10.08 08:01:16 (GMT+08:00)</v>
+        <v>2024.09.29 08:30:41 (GMT+08:00)</v>
       </c>
       <c r="V5" t="str">
-        <v>2024.10.08 17:03:26 (GMT+08:00)</v>
+        <v>2024.09.29 23:27:07 (GMT+08:00)</v>
       </c>
       <c r="W5" t="str">
-        <v>09:02:10</v>
+        <v>14:56:26</v>
       </c>
       <c r="X5" t="str">
-        <v>与服务器连接意外中断</v>
+        <v>主动挂断</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>鹿文杰</v>
-      </c>
-      <c r="B6" t="str"/>
+        <v>小王</v>
+      </c>
+      <c r="B6" t="str">
+        <v>飞书个人用户</v>
+      </c>
       <c r="C6" t="str"/>
       <c r="D6" t="str"/>
       <c r="E6" t="str"/>
@@ -680,13 +680,13 @@
         <v>ANDROID</v>
       </c>
       <c r="H6" t="str">
-        <v>7.27.6</v>
+        <v>7.26.6</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
       </c>
       <c r="J6" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="K6" t="str">
         <v>否</v>
@@ -704,7 +704,7 @@
         <v>不支持查看外部参会者的敏感信息</v>
       </c>
       <c r="P6" t="str">
-        <v>wifi</v>
+        <v>5G</v>
       </c>
       <c r="Q6" t="str">
         <v>udp</v>
@@ -719,13 +719,13 @@
         <v>front_camera</v>
       </c>
       <c r="U6" t="str">
-        <v>2024.10.08 08:07:53 (GMT+08:00)</v>
+        <v>2024.09.29 08:31:23 (GMT+08:00)</v>
       </c>
       <c r="V6" t="str">
-        <v>2024.10.08 23:11:54 (GMT+08:00)</v>
+        <v>2024.09.29 14:59:26 (GMT+08:00)</v>
       </c>
       <c r="W6" t="str">
-        <v>15:04:01</v>
+        <v>06:28:03</v>
       </c>
       <c r="X6" t="str">
         <v>主动挂断</v>
@@ -775,9 +775,7 @@
       <c r="Q7" t="str">
         <v>udp</v>
       </c>
-      <c r="R7" t="str">
-        <v>MicrophoneBuiltIn</v>
-      </c>
+      <c r="R7" t="str"/>
       <c r="S7" t="str">
         <v>Speaker</v>
       </c>
@@ -785,13 +783,13 @@
         <v>后置相机</v>
       </c>
       <c r="U7" t="str">
-        <v>2024.10.08 08:18:27 (GMT+08:00)</v>
+        <v>2024.09.29 08:47:58 (GMT+08:00)</v>
       </c>
       <c r="V7" t="str">
-        <v>2024.10.08 18:01:36 (GMT+08:00)</v>
+        <v>2024.09.29 17:08:53 (GMT+08:00)</v>
       </c>
       <c r="W7" t="str">
-        <v>09:43:09</v>
+        <v>08:20:55</v>
       </c>
       <c r="X7" t="str">
         <v>主动挂断</v>
@@ -799,11 +797,9 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>xiaozhi</v>
-      </c>
-      <c r="B8" t="str">
-        <v>飞书个人用户</v>
-      </c>
+        <v>赫赫有名</v>
+      </c>
+      <c r="B8" t="str"/>
       <c r="C8" t="str"/>
       <c r="D8" t="str"/>
       <c r="E8" t="str"/>
@@ -814,13 +810,13 @@
         <v>ANDROID</v>
       </c>
       <c r="H8" t="str">
-        <v>7.27.6</v>
+        <v>7.26.6</v>
       </c>
       <c r="I8" t="str">
         <v>否</v>
       </c>
       <c r="J8" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="K8" t="str">
         <v>否</v>
@@ -838,7 +834,7 @@
         <v>不支持查看外部参会者的敏感信息</v>
       </c>
       <c r="P8" t="str">
-        <v>5G</v>
+        <v>wifi</v>
       </c>
       <c r="Q8" t="str">
         <v>udp</v>
@@ -853,23 +849,25 @@
         <v>front_camera</v>
       </c>
       <c r="U8" t="str">
-        <v>2024.10.08 10:25:52 (GMT+08:00)</v>
+        <v>2024.09.29 09:16:30 (GMT+08:00)</v>
       </c>
       <c r="V8" t="str">
-        <v>2024.10.08 22:03:04 (GMT+08:00)</v>
+        <v>2024.09.29 15:52:40 (GMT+08:00)</v>
       </c>
       <c r="W8" t="str">
-        <v>11:37:12</v>
+        <v>06:36:10</v>
       </c>
       <c r="X8" t="str">
-        <v>与服务器连接意外中断</v>
+        <v>主动挂断</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>毛茸茸</v>
-      </c>
-      <c r="B9" t="str"/>
+        <v>吴圣源</v>
+      </c>
+      <c r="B9" t="str">
+        <v>飞书个人用户</v>
+      </c>
       <c r="C9" t="str"/>
       <c r="D9" t="str"/>
       <c r="E9" t="str"/>
@@ -877,10 +875,10 @@
         <v>-</v>
       </c>
       <c r="G9" t="str">
-        <v>IPHONE</v>
+        <v>WINDOWS</v>
       </c>
       <c r="H9" t="str">
-        <v>7.26.15</v>
+        <v>7.27.8</v>
       </c>
       <c r="I9" t="str">
         <v>否</v>
@@ -910,22 +908,22 @@
         <v>udp</v>
       </c>
       <c r="R9" t="str">
-        <v>MicrophoneBuiltIn</v>
+        <v>与系统一致（麦克风阵列 (Realtek(R) Audio)）</v>
       </c>
       <c r="S9" t="str">
-        <v>Speaker</v>
+        <v>与系统一致（扬声器 (Realtek(R) Audio)）</v>
       </c>
       <c r="T9" t="str">
-        <v>前置相机</v>
+        <v>HD Camera</v>
       </c>
       <c r="U9" t="str">
-        <v>2024.10.08 14:01:37 (GMT+08:00)</v>
+        <v>2024.09.29 14:05:04 (GMT+08:00)</v>
       </c>
       <c r="V9" t="str">
-        <v>2024.10.08 22:32:47 (GMT+08:00)</v>
+        <v>2024.09.29 17:31:47 (GMT+08:00)</v>
       </c>
       <c r="W9" t="str">
-        <v>08:31:10</v>
+        <v>03:26:43</v>
       </c>
       <c r="X9" t="str">
         <v>主动挂断</v>
@@ -933,7 +931,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>赫赫有名</v>
+        <v>七七七学习了没(七七)</v>
       </c>
       <c r="B10" t="str"/>
       <c r="C10" t="str"/>
@@ -985,13 +983,13 @@
         <v>front_camera</v>
       </c>
       <c r="U10" t="str">
-        <v>2024.10.08 15:58:43 (GMT+08:00)</v>
+        <v>2024.09.29 14:16:06 (GMT+08:00)</v>
       </c>
       <c r="V10" t="str">
-        <v>2024.10.08 20:35:53 (GMT+08:00)</v>
+        <v>2024.09.29 23:22:20 (GMT+08:00)</v>
       </c>
       <c r="W10" t="str">
-        <v>04:37:10</v>
+        <v>09:06:14</v>
       </c>
       <c r="X10" t="str">
         <v>主动挂断</v>
@@ -1009,7 +1007,7 @@
         <v>-</v>
       </c>
       <c r="G11" t="str">
-        <v>WINDOWS</v>
+        <v>ANDROID</v>
       </c>
       <c r="H11" t="str">
         <v>7.26.6</v>
@@ -1018,7 +1016,7 @@
         <v>否</v>
       </c>
       <c r="J11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="K11" t="str">
         <v>否</v>
@@ -1036,28 +1034,28 @@
         <v>不支持查看外部参会者的敏感信息</v>
       </c>
       <c r="P11" t="str">
-        <v>wifi</v>
+        <v>4G</v>
       </c>
       <c r="Q11" t="str">
         <v>udp</v>
       </c>
       <c r="R11" t="str">
-        <v>Same as system (麦克风 (Realtek(R) Audio))</v>
+        <v>MicrophoneBuiltIn</v>
       </c>
       <c r="S11" t="str">
-        <v>Same as system (耳机 (Realtek(R) Audio))</v>
+        <v>SpeakerBuiltIn</v>
       </c>
       <c r="T11" t="str">
-        <v>XiaoMi USB 2.0 Webcam</v>
+        <v>front_camera</v>
       </c>
       <c r="U11" t="str">
-        <v>2024.10.08 15:59:17 (GMT+08:00)</v>
+        <v>2024.09.29 14:16:44 (GMT+08:00)</v>
       </c>
       <c r="V11" t="str">
-        <v>2024.10.09 00:30:23 (GMT+08:00)</v>
+        <v>2024.09.29 22:44:46 (GMT+08:00)</v>
       </c>
       <c r="W11" t="str">
-        <v>08:31:06</v>
+        <v>08:28:02</v>
       </c>
       <c r="X11" t="str">
         <v>主动挂断</v>
@@ -1065,12 +1063,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>孙笑川</v>
+        <v>果果</v>
       </c>
       <c r="B12" t="str"/>
-      <c r="C12" t="str"/>
+      <c r="C12" t="str">
+        <v>3bgda3d2</v>
+      </c>
       <c r="D12" t="str"/>
-      <c r="E12" t="str"/>
+      <c r="E12" t="str">
+        <v>+86135****5921</v>
+      </c>
       <c r="F12" t="str">
         <v>-</v>
       </c>
@@ -1090,40 +1092,34 @@
         <v>否</v>
       </c>
       <c r="L12" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
+        <v>240a:42cd:fe01:b2a:17f9:8c59:135d:a1cf</v>
       </c>
       <c r="M12" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
+        <v>127.0.0.1</v>
       </c>
       <c r="N12" t="str">
         <v>否</v>
       </c>
       <c r="O12" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
+        <v>阳江(中国大陆)</v>
       </c>
       <c r="P12" t="str">
-        <v>wifi</v>
+        <v>5G</v>
       </c>
       <c r="Q12" t="str">
         <v>udp</v>
       </c>
-      <c r="R12" t="str">
-        <v>MicrophoneBuiltIn</v>
-      </c>
-      <c r="S12" t="str">
-        <v>SpeakerBuiltIn</v>
-      </c>
-      <c r="T12" t="str">
-        <v>front_camera</v>
-      </c>
+      <c r="R12" t="str"/>
+      <c r="S12" t="str"/>
+      <c r="T12" t="str"/>
       <c r="U12" t="str">
-        <v>2024.10.08 16:10:44 (GMT+08:00)</v>
+        <v>2024.09.29 14:56:24 (GMT+08:00)</v>
       </c>
       <c r="V12" t="str">
-        <v>2024.10.08 16:10:57 (GMT+08:00)</v>
+        <v>2024.09.29 14:57:48 (GMT+08:00)</v>
       </c>
       <c r="W12" t="str">
-        <v>00:00:13</v>
+        <v>00:01:24</v>
       </c>
       <c r="X12" t="str">
         <v>主动挂断</v>
@@ -1131,7 +1127,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ielts</v>
+        <v>辛烨</v>
       </c>
       <c r="B13" t="str"/>
       <c r="C13" t="str"/>
@@ -1141,10 +1137,10 @@
         <v>-</v>
       </c>
       <c r="G13" t="str">
-        <v>IPAD</v>
+        <v>ANDROID</v>
       </c>
       <c r="H13" t="str">
-        <v>7.27.14</v>
+        <v>7.27.6</v>
       </c>
       <c r="I13" t="str">
         <v>否</v>
@@ -1177,27 +1173,27 @@
         <v>MicrophoneBuiltIn</v>
       </c>
       <c r="S13" t="str">
-        <v>Speaker</v>
+        <v>SpeakerBuiltIn</v>
       </c>
       <c r="T13" t="str">
-        <v>前置相机</v>
+        <v>front_camera</v>
       </c>
       <c r="U13" t="str">
-        <v>2024.10.08 16:14:04 (GMT+08:00)</v>
+        <v>2024.09.29 20:16:53 (GMT+08:00)</v>
       </c>
       <c r="V13" t="str">
-        <v>2024.10.08 20:30:08 (GMT+08:00)</v>
+        <v>2024.09.29 20:26:39 (GMT+08:00)</v>
       </c>
       <c r="W13" t="str">
-        <v>04:16:04</v>
+        <v>00:09:46</v>
       </c>
       <c r="X13" t="str">
-        <v>与服务器连接意外中断</v>
+        <v>主动挂断</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>论文</v>
+        <v>飞书用户7802BS(龙🐲)</v>
       </c>
       <c r="B14" t="str"/>
       <c r="C14" t="str"/>
@@ -1207,16 +1203,16 @@
         <v>-</v>
       </c>
       <c r="G14" t="str">
-        <v>IPHONE</v>
+        <v>ANDROID</v>
       </c>
       <c r="H14" t="str">
-        <v>7.27.14</v>
+        <v>7.27.6</v>
       </c>
       <c r="I14" t="str">
         <v>否</v>
       </c>
       <c r="J14" t="str">
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="K14" t="str">
         <v>否</v>
@@ -1243,288 +1239,22 @@
         <v>MicrophoneBuiltIn</v>
       </c>
       <c r="S14" t="str">
-        <v>Speaker</v>
+        <v>SpeakerBuiltIn</v>
       </c>
       <c r="T14" t="str">
-        <v>前置相机</v>
+        <v>front_camera</v>
       </c>
       <c r="U14" t="str">
-        <v>2024.10.08 17:10:00 (GMT+08:00)</v>
+        <v>2024.09.29 20:43:22 (GMT+08:00)</v>
       </c>
       <c r="V14" t="str">
-        <v>2024.10.08 21:47:33 (GMT+08:00)</v>
+        <v>2024.09.29 21:37:35 (GMT+08:00)</v>
       </c>
       <c r="W14" t="str">
-        <v>04:37:33</v>
+        <v>00:54:13</v>
       </c>
       <c r="X14" t="str">
-        <v>主动挂断</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>张劲松</v>
-      </c>
-      <c r="B15" t="str"/>
-      <c r="C15" t="str"/>
-      <c r="D15" t="str"/>
-      <c r="E15" t="str"/>
-      <c r="F15" t="str">
-        <v>-</v>
-      </c>
-      <c r="G15" t="str">
-        <v>ANDROID</v>
-      </c>
-      <c r="H15" t="str">
-        <v>7.27.6</v>
-      </c>
-      <c r="I15" t="str">
-        <v>否</v>
-      </c>
-      <c r="J15" t="str">
-        <v>否</v>
-      </c>
-      <c r="K15" t="str">
-        <v>否</v>
-      </c>
-      <c r="L15" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="M15" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="N15" t="str">
-        <v>否</v>
-      </c>
-      <c r="O15" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="P15" t="str">
-        <v>wifi</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>udp</v>
-      </c>
-      <c r="R15" t="str">
-        <v>MicrophoneBuiltIn</v>
-      </c>
-      <c r="S15" t="str">
-        <v>SpeakerBuiltIn</v>
-      </c>
-      <c r="T15" t="str">
-        <v>front_camera</v>
-      </c>
-      <c r="U15" t="str">
-        <v>2024.10.08 19:33:01 (GMT+08:00)</v>
-      </c>
-      <c r="V15" t="str">
-        <v>2024.10.08 19:53:37 (GMT+08:00)</v>
-      </c>
-      <c r="W15" t="str">
-        <v>00:20:36</v>
-      </c>
-      <c r="X15" t="str">
         <v>与服务器连接意外中断</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>zzz</v>
-      </c>
-      <c r="B16" t="str"/>
-      <c r="C16" t="str"/>
-      <c r="D16" t="str"/>
-      <c r="E16" t="str"/>
-      <c r="F16" t="str">
-        <v>-</v>
-      </c>
-      <c r="G16" t="str">
-        <v>ANDROID</v>
-      </c>
-      <c r="H16" t="str">
-        <v>7.27.6</v>
-      </c>
-      <c r="I16" t="str">
-        <v>否</v>
-      </c>
-      <c r="J16" t="str">
-        <v>是</v>
-      </c>
-      <c r="K16" t="str">
-        <v>否</v>
-      </c>
-      <c r="L16" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="M16" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="N16" t="str">
-        <v>否</v>
-      </c>
-      <c r="O16" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="P16" t="str">
-        <v>wifi</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>udp</v>
-      </c>
-      <c r="R16" t="str">
-        <v>MicrophoneBuiltIn</v>
-      </c>
-      <c r="S16" t="str">
-        <v>SpeakerBuiltIn</v>
-      </c>
-      <c r="T16" t="str">
-        <v>front_camera</v>
-      </c>
-      <c r="U16" t="str">
-        <v>2024.10.08 21:24:38 (GMT+08:00)</v>
-      </c>
-      <c r="V16" t="str">
-        <v>2024.10.08 22:37:32 (GMT+08:00)</v>
-      </c>
-      <c r="W16" t="str">
-        <v>01:12:54</v>
-      </c>
-      <c r="X16" t="str">
-        <v>主动挂断</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Shareway</v>
-      </c>
-      <c r="B17" t="str">
-        <v>飞书个人用户</v>
-      </c>
-      <c r="C17" t="str"/>
-      <c r="D17" t="str"/>
-      <c r="E17" t="str"/>
-      <c r="F17" t="str">
-        <v>-</v>
-      </c>
-      <c r="G17" t="str">
-        <v>MAC</v>
-      </c>
-      <c r="H17" t="str">
-        <v>7.23.18</v>
-      </c>
-      <c r="I17" t="str">
-        <v>否</v>
-      </c>
-      <c r="J17" t="str">
-        <v>是</v>
-      </c>
-      <c r="K17" t="str">
-        <v>否</v>
-      </c>
-      <c r="L17" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="M17" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="N17" t="str">
-        <v>否</v>
-      </c>
-      <c r="O17" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="P17" t="str">
-        <v>wifi</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>udp</v>
-      </c>
-      <c r="R17" t="str">
-        <v>与系统一致（MacBook Pro麦克风）</v>
-      </c>
-      <c r="S17" t="str">
-        <v>与系统一致（MacBook Pro扬声器）</v>
-      </c>
-      <c r="T17" t="str">
-        <v>FaceTime高清摄像头</v>
-      </c>
-      <c r="U17" t="str">
-        <v>2024.10.08 21:45:14 (GMT+08:00)</v>
-      </c>
-      <c r="V17" t="str">
-        <v>2024.10.08 22:06:37 (GMT+08:00)</v>
-      </c>
-      <c r="W17" t="str">
-        <v>00:21:23</v>
-      </c>
-      <c r="X17" t="str">
-        <v>主动挂断</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>李德胜</v>
-      </c>
-      <c r="B18" t="str"/>
-      <c r="C18" t="str"/>
-      <c r="D18" t="str"/>
-      <c r="E18" t="str"/>
-      <c r="F18" t="str">
-        <v>-</v>
-      </c>
-      <c r="G18" t="str">
-        <v>WINDOWS</v>
-      </c>
-      <c r="H18" t="str">
-        <v>7.28.2</v>
-      </c>
-      <c r="I18" t="str">
-        <v>否</v>
-      </c>
-      <c r="J18" t="str">
-        <v>否</v>
-      </c>
-      <c r="K18" t="str">
-        <v>否</v>
-      </c>
-      <c r="L18" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="M18" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="N18" t="str">
-        <v>否</v>
-      </c>
-      <c r="O18" t="str">
-        <v>不支持查看外部参会者的敏感信息</v>
-      </c>
-      <c r="P18" t="str">
-        <v>wifi</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>udp</v>
-      </c>
-      <c r="R18" t="str">
-        <v>与系统一致（麦克风阵列 (适用于数字麦克风的英特尔® 智音技术)）</v>
-      </c>
-      <c r="S18" t="str">
-        <v>与系统一致（扬声器 (Realtek(R) Audio)）</v>
-      </c>
-      <c r="T18" t="str">
-        <v>XiaoMi USB 2.0 Webcam</v>
-      </c>
-      <c r="U18" t="str">
-        <v>2024.10.09 00:11:04 (GMT+08:00)</v>
-      </c>
-      <c r="V18" t="str">
-        <v>2024.10.09 00:35:23 (GMT+08:00)</v>
-      </c>
-      <c r="W18" t="str">
-        <v>00:24:19</v>
-      </c>
-      <c r="X18" t="str">
-        <v>主动挂断</v>
       </c>
     </row>
   </sheetData>
